--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486880_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486880_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7377</v>
+        <v>8.225899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1006</v>
+        <v>8.1738</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3629</v>
+        <v>0.0521</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2452</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4824</v>
+        <v>0.0058</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6860000000000001</v>
+        <v>0.3872</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7964</v>
+        <v>-0.3814</v>
       </c>
       <c r="V2" t="n">
         <v>6.8225</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>R. TIMONER GIMENEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1856</v>
+        <v>1.2382</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4863</v>
+        <v>1.1211</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3008</v>
+        <v>0.1171</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8246</v>
+        <v>-0.104</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2296</v>
+        <v>-2.2221</v>
       </c>
       <c r="I3" t="n">
-        <v>0.595</v>
+        <v>2.1181</v>
       </c>
       <c r="J3" t="n">
-        <v>2.342</v>
+        <v>0.6947</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1447</v>
+        <v>-1.002</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1973</v>
+        <v>1.6967</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5174</v>
+        <v>-0.7987</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9151</v>
+        <v>-1.2201</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3977</v>
+        <v>0.4215</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.6427</v>
+        <v>0.616</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1216</v>
+        <v>0.495</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8672</v>
+        <v>0.3833</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2544</v>
+        <v>0.1116</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1179</v>
+        <v>0.2312</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3573</v>
+        <v>1.0698</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4751</v>
+        <v>-0.8386</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. CADME ARIAS</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5875</v>
+        <v>0.8776</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4055</v>
+        <v>2.297</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8181</v>
+        <v>-1.4193</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0685</v>
+        <v>1.8246</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9339</v>
+        <v>1.2296</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0024</v>
+        <v>0.595</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9989</v>
+        <v>2.342</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0915</v>
+        <v>2.1447</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9074</v>
+        <v>0.1973</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9305</v>
+        <v>-0.5174</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0255</v>
+        <v>-0.9151</v>
       </c>
       <c r="O4" t="n">
-        <v>0.095</v>
+        <v>0.3977</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6427</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6427</v>
+        <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3514</v>
+        <v>0.8136</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4066</v>
+        <v>0.6778</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0552</v>
+        <v>0.1358</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.4751</v>
+        <v>-0.1179</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="X4" t="n">
         <v>-2.4751</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>G. CADME ARIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5397</v>
+        <v>0.3939</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3156</v>
+        <v>2.3009</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7759</v>
+        <v>-1.907</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3008</v>
+        <v>1.0685</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1162</v>
+        <v>-0.9339</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8154</v>
+        <v>2.0024</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2105</v>
+        <v>1.9989</v>
       </c>
       <c r="K5" t="n">
-        <v>0.75</v>
+        <v>0.0915</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5395</v>
+        <v>1.9074</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.9305</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3662</v>
+        <v>-1.0255</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2759</v>
+        <v>0.095</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3781</v>
+        <v>0.1579</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7746</v>
+        <v>0.302</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6035</v>
+        <v>-0.1442</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.3445</v>
+        <v>-2.4751</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.7018</v>
+        <v>-2.4751</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.32</v>
+        <v>-0.2311</v>
       </c>
       <c r="E6" t="n">
         <v>-0.9873</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6673</v>
+        <v>0.7562</v>
       </c>
       <c r="G6" t="n">
         <v>-0.08160000000000001</v>
@@ -922,13 +922,13 @@
         <v>0.4107</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4831</v>
+        <v>-0.3942</v>
       </c>
       <c r="T6" t="n">
         <v>-0.2635</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2197</v>
+        <v>-0.1307</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1659</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. TIMONER GIMENEZ</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.2369</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5138</v>
+        <v>1.9244</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0311</v>
+        <v>-2.1613</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.104</v>
+        <v>0.3008</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2221</v>
+        <v>1.1162</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1181</v>
+        <v>-0.8154</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6947</v>
+        <v>0.2105</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.002</v>
+        <v>0.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6967</v>
+        <v>-0.5395</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7987</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2201</v>
+        <v>0.3662</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4215</v>
+        <v>-0.2759</v>
       </c>
       <c r="P7" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2882</v>
+        <v>0.6015</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2516</v>
+        <v>0.3833</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0366</v>
+        <v>0.2181</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2312</v>
+        <v>-1.3445</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0698</v>
+        <v>2.3573</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8386</v>
+        <v>-3.7018</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1227</v>
+        <v>-1.2891</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.443</v>
+        <v>-2.5205</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3203</v>
+        <v>1.2314</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3949</v>
@@ -1078,13 +1078,13 @@
         <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>1.041</v>
+        <v>0.8746</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9064</v>
+        <v>0.8289</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1347</v>
+        <v>0.0457</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3581</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9949</v>
+        <v>-2.1086</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7943</v>
+        <v>-0.9377</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2006</v>
+        <v>-1.171</v>
       </c>
       <c r="G9" t="n">
         <v>1.1974</v>
@@ -1156,13 +1156,13 @@
         <v>0.8214</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3755</v>
+        <v>-0.4892</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0272</v>
+        <v>-0.1706</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3482</v>
+        <v>-0.3186</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5848</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6643</v>
+        <v>-3.0977</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0269</v>
+        <v>-3.6085</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3626</v>
+        <v>0.5108</v>
       </c>
       <c r="G10" t="n">
         <v>-3.3616</v>
@@ -1234,13 +1234,13 @@
         <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1101</v>
+        <v>-0.5434</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7905</v>
+        <v>-0.3721</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3196</v>
+        <v>-0.1714</v>
       </c>
       <c r="V10" t="n">
         <v>1.0127</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2496</v>
+        <v>-4.757</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4556</v>
+        <v>-2.8741</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.794</v>
+        <v>-1.8829</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6355</v>
@@ -1312,13 +1312,13 @@
         <v>0.4107</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3858</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0653</v>
+        <v>0.6469</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3205</v>
+        <v>0.2316</v>
       </c>
       <c r="V11" t="n">
         <v>-2.3573</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6407</v>
+        <v>-6.8433</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.656</v>
+        <v>-1.7994</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.9846</v>
+        <v>-5.0439</v>
       </c>
       <c r="G12" t="n">
         <v>0.2208</v>
@@ -1390,13 +1390,13 @@
         <v>0.616</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4348</v>
+        <v>-0.6374</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0272</v>
+        <v>-0.1706</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4075</v>
+        <v>-0.4668</v>
       </c>
       <c r="V12" t="n">
         <v>-4.9893</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.486599999999999</v>
+        <v>-7.828100000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4311</v>
+        <v>3.089700000000001</v>
       </c>
       <c r="F13" t="n">
         <v>-10.9178</v>
@@ -1453,7 +1453,7 @@
         <v>-3.4649</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.4151</v>
+        <v>-4.415099999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0.9500999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>12.3205</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1038</v>
+        <v>1.7627</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9741</v>
+        <v>2.6326</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8701000000000001</v>
+        <v>-0.8703</v>
       </c>
       <c r="V13" t="n">
         <v>-5.326499999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.523300000000001</v>
+        <v>10.2572</v>
       </c>
       <c r="E14" t="n">
-        <v>8.788600000000001</v>
+        <v>9.73</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7347</v>
+        <v>0.5272</v>
       </c>
       <c r="G14" t="n">
         <v>7.3696</v>
@@ -1546,13 +1546,13 @@
         <v>1.8481</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5485</v>
+        <v>-0.8146</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3756</v>
+        <v>-0.4342</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1729</v>
+        <v>-0.3804</v>
       </c>
       <c r="V14" t="n">
         <v>3.9075</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.5321</v>
+        <v>7.0694</v>
       </c>
       <c r="E15" t="n">
-        <v>7.0751</v>
+        <v>5.8198</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4571</v>
+        <v>1.2496</v>
       </c>
       <c r="G15" t="n">
         <v>1.531</v>
@@ -1624,13 +1624,13 @@
         <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>2.0546</v>
+        <v>0.5918</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8749</v>
+        <v>0.6197</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1796</v>
+        <v>-0.0279</v>
       </c>
       <c r="V15" t="n">
         <v>4.1252</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.199</v>
+        <v>2.5128</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3497</v>
+        <v>1.6635</v>
       </c>
       <c r="F16" t="n">
         <v>0.8493000000000001</v>
@@ -1702,10 +1702,10 @@
         <v>1.4374</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3603</v>
+        <v>-0.0465</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4611</v>
+        <v>-0.1473</v>
       </c>
       <c r="U16" t="n">
         <v>0.1008</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. GARRIDO TEBAN</t>
+          <t>N. FERRER IGLESIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0372</v>
+        <v>1.2333</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2329</v>
+        <v>0.8137</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1957</v>
+        <v>0.4196</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0673</v>
+        <v>1.0715</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6323</v>
+        <v>-0.052</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6997</v>
+        <v>1.1234</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3838</v>
+        <v>0.624</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1557</v>
+        <v>0.0584</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5395</v>
+        <v>0.5656</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3164</v>
+        <v>0.4475</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4766</v>
+        <v>-0.1104</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1602</v>
+        <v>0.5579</v>
       </c>
       <c r="P17" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6819</v>
+        <v>0.3138</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1513</v>
+        <v>0.1898</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5306</v>
+        <v>0.124</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3491</v>
+        <v>-1.1786</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. ACOSTA ALMONTE</t>
+          <t>F. GARRIDO TEBAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9348</v>
+        <v>1.0372</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6315</v>
+        <v>1.2329</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3033</v>
+        <v>-0.1957</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5579</v>
+        <v>-0.0673</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2789</v>
+        <v>0.6323</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2789</v>
+        <v>-0.6997</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.3838</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.1557</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.5395</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5579</v>
+        <v>0.3164</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2789</v>
+        <v>0.4766</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2789</v>
+        <v>-0.1602</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4118</v>
+        <v>-0.6819</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6315</v>
+        <v>-0.1513</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2197</v>
+        <v>-0.5306</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2402</v>
+        <v>0.3491</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.7679</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2402</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. FERRER IGLESIA</t>
+          <t>D. ACOSTA ALMONTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.801</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4999</v>
+        <v>0.2131</v>
       </c>
       <c r="F19" t="n">
-        <v>0.301</v>
+        <v>0.3923</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0715</v>
+        <v>0.5579</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.052</v>
+        <v>0.2789</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1234</v>
+        <v>0.2789</v>
       </c>
       <c r="J19" t="n">
-        <v>0.624</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0584</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5656</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4475</v>
+        <v>0.5579</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1104</v>
+        <v>0.2789</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5579</v>
+        <v>0.2789</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0267</v>
+        <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1186</v>
+        <v>0.0823</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.124</v>
+        <v>0.2131</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0054</v>
+        <v>-0.1307</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>G. MARTINEZ RIVERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1769</v>
+        <v>-0.3397</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2797</v>
+        <v>1.2015</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4565</v>
+        <v>-1.5412</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5772</v>
+        <v>-0.3901</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1493</v>
+        <v>0.9831</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7265</v>
+        <v>-1.3733</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6364</v>
+        <v>-0.1754</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3996</v>
+        <v>0.3641</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2368</v>
+        <v>-0.5395</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0592</v>
+        <v>-0.2147</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5489000000000001</v>
+        <v>0.6191</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4897</v>
+        <v>-0.8338</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S20" t="n">
-        <v>1.747</v>
+        <v>-0.8058</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2512</v>
+        <v>-0.1939</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4958</v>
+        <v>-0.612</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.7063</v>
+        <v>0.2402</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4189</v>
+        <v>2.5975</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.1252</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. MARTINEZ RIVERA</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2184</v>
+        <v>-1.1305</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6785</v>
+        <v>1.6521</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8969</v>
+        <v>-2.7826</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3901</v>
+        <v>0.5772</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9831</v>
+        <v>-0.1493</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3733</v>
+        <v>0.7265</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1754</v>
+        <v>0.6364</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3641</v>
+        <v>0.3996</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5395</v>
+        <v>0.2368</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2147</v>
+        <v>-0.0592</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6191</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8338</v>
+        <v>0.4897</v>
       </c>
       <c r="P21" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6845</v>
+        <v>0.7933</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7169</v>
+        <v>0.6236</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9677</v>
+        <v>0.1698</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2402</v>
+        <v>-2.7063</v>
       </c>
       <c r="W21" t="n">
-        <v>2.5975</v>
+        <v>1.4189</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.3573</v>
+        <v>-4.1252</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9627</v>
+        <v>-2.5886</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8594</v>
+        <v>-2.2778</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1033</v>
+        <v>-0.3108</v>
       </c>
       <c r="G22" t="n">
         <v>-4.5911</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8071</v>
+        <v>0.1811</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6778</v>
+        <v>0.2594</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1292</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0.5893</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4552</v>
+        <v>-3.1711</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3292</v>
+        <v>-4.0154</v>
       </c>
       <c r="F23" t="n">
-        <v>0.874</v>
+        <v>0.8444</v>
       </c>
       <c r="G23" t="n">
         <v>-1.9826</v>
@@ -2248,13 +2248,13 @@
         <v>0.616</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0352</v>
+        <v>0.249</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3216</v>
+        <v>-0.0078</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2864</v>
+        <v>0.2568</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.7275</v>
+        <v>-6.9987</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4295</v>
+        <v>-5.1157</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2981</v>
+        <v>-1.8831</v>
       </c>
       <c r="G24" t="n">
         <v>-2.5947</v>
@@ -2326,13 +2326,13 @@
         <v>1.8481</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6954</v>
+        <v>-0.9666</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4147</v>
+        <v>-0.1009</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2807</v>
+        <v>-0.8657</v>
       </c>
       <c r="V24" t="n">
         <v>-1.1786</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8.486699999999995</v>
+        <v>8.486599999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>10.9178</v>
+        <v>10.9177</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4311</v>
+        <v>-2.431</v>
       </c>
       <c r="G25" t="n">
         <v>2.211100000000001</v>
@@ -2374,10 +2374,10 @@
         <v>6.2761</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.0654</v>
+        <v>-4.065399999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>3.464900000000002</v>
+        <v>3.4649</v>
       </c>
       <c r="K25" t="n">
         <v>4.4152</v>
@@ -2404,16 +2404,16 @@
         <v>14.374</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1039</v>
+        <v>-1.1041</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8701999999999999</v>
+        <v>0.8702000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.9744</v>
+        <v>-1.9742</v>
       </c>
       <c r="V25" t="n">
-        <v>5.3265</v>
+        <v>5.326499999999999</v>
       </c>
       <c r="W25" t="n">
         <v>18.9031</v>
